--- a/artfynd/A 60361-2025 artfynd.xlsx
+++ b/artfynd/A 60361-2025 artfynd.xlsx
@@ -3034,10 +3034,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130141164</v>
+        <v>130141057</v>
       </c>
       <c r="B24" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3045,34 +3045,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>407944</v>
+        <v>407845</v>
       </c>
       <c r="R24" t="n">
-        <v>6772271</v>
+        <v>6772259</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3104,7 +3109,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3114,7 +3119,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3141,7 +3146,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130141155</v>
+        <v>130141164</v>
       </c>
       <c r="B25" t="n">
         <v>79095</v>
@@ -3176,10 +3181,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>407860</v>
+        <v>407944</v>
       </c>
       <c r="R25" t="n">
-        <v>6772289</v>
+        <v>6772271</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3211,7 +3216,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3221,7 +3226,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3248,10 +3253,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130141057</v>
+        <v>130141155</v>
       </c>
       <c r="B26" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3259,39 +3264,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>407845</v>
+        <v>407860</v>
       </c>
       <c r="R26" t="n">
-        <v>6772259</v>
+        <v>6772289</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3323,7 +3323,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 60361-2025 artfynd.xlsx
+++ b/artfynd/A 60361-2025 artfynd.xlsx
@@ -1317,32 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130141085</v>
+        <v>130141199</v>
       </c>
       <c r="B8" t="n">
-        <v>95681</v>
+        <v>89038</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2387</v>
+        <v>510</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>407835</v>
+        <v>407972</v>
       </c>
       <c r="R8" t="n">
-        <v>6772263</v>
+        <v>6772290</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,32 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130141199</v>
+        <v>130141085</v>
       </c>
       <c r="B9" t="n">
-        <v>89038</v>
+        <v>95681</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>510</v>
+        <v>2387</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>407972</v>
+        <v>407835</v>
       </c>
       <c r="R9" t="n">
-        <v>6772290</v>
+        <v>6772263</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 60361-2025 artfynd.xlsx
+++ b/artfynd/A 60361-2025 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>130141067</v>
       </c>
       <c r="B5" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130141199</v>
+        <v>130141162</v>
       </c>
       <c r="B8" t="n">
-        <v>89038</v>
+        <v>79095</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>407972</v>
+        <v>407915</v>
       </c>
       <c r="R8" t="n">
-        <v>6772290</v>
+        <v>6772325</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,32 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130141085</v>
+        <v>130141157</v>
       </c>
       <c r="B9" t="n">
-        <v>95681</v>
+        <v>79095</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2387</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>407835</v>
+        <v>407868</v>
       </c>
       <c r="R9" t="n">
-        <v>6772263</v>
+        <v>6772318</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130141162</v>
+        <v>130141199</v>
       </c>
       <c r="B10" t="n">
-        <v>79095</v>
+        <v>89038</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>407915</v>
+        <v>407972</v>
       </c>
       <c r="R10" t="n">
-        <v>6772325</v>
+        <v>6772290</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,32 +1638,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130141157</v>
+        <v>130141085</v>
       </c>
       <c r="B11" t="n">
-        <v>79095</v>
+        <v>95683</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2387</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>407868</v>
+        <v>407835</v>
       </c>
       <c r="R11" t="n">
-        <v>6772318</v>
+        <v>6772263</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1748,7 +1748,7 @@
         <v>130141058</v>
       </c>
       <c r="B12" t="n">
-        <v>91412</v>
+        <v>91414</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2071,32 +2071,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130141165</v>
+        <v>130141066</v>
       </c>
       <c r="B15" t="n">
-        <v>79095</v>
+        <v>97704</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>407950</v>
+        <v>407860</v>
       </c>
       <c r="R15" t="n">
-        <v>6772269</v>
+        <v>6772255</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2178,32 +2178,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130141066</v>
+        <v>130141165</v>
       </c>
       <c r="B16" t="n">
-        <v>97702</v>
+        <v>79095</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2213,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407860</v>
+        <v>407950</v>
       </c>
       <c r="R16" t="n">
-        <v>6772255</v>
+        <v>6772269</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2392,7 +2392,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130141158</v>
+        <v>130141148</v>
       </c>
       <c r="B18" t="n">
         <v>79095</v>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>407887</v>
+        <v>407876</v>
       </c>
       <c r="R18" t="n">
-        <v>6772324</v>
+        <v>6772259</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2499,7 +2499,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130141148</v>
+        <v>130141160</v>
       </c>
       <c r="B19" t="n">
         <v>79095</v>
@@ -2534,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>407876</v>
+        <v>407893</v>
       </c>
       <c r="R19" t="n">
-        <v>6772259</v>
+        <v>6772324</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2606,7 +2606,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130141160</v>
+        <v>130141158</v>
       </c>
       <c r="B20" t="n">
         <v>79095</v>
@@ -2641,7 +2641,7 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>407893</v>
+        <v>407887</v>
       </c>
       <c r="R20" t="n">
         <v>6772324</v>
@@ -2716,7 +2716,7 @@
         <v>130141047</v>
       </c>
       <c r="B21" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>130141036</v>
       </c>
       <c r="B22" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 60361-2025 artfynd.xlsx
+++ b/artfynd/A 60361-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130141147</v>
       </c>
       <c r="B2" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130141156</v>
       </c>
       <c r="B3" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>130141152</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>130141067</v>
       </c>
       <c r="B5" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>130141144</v>
       </c>
       <c r="B6" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>130141161</v>
       </c>
       <c r="B7" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>130141162</v>
       </c>
       <c r="B8" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130141157</v>
+        <v>130141199</v>
       </c>
       <c r="B9" t="n">
-        <v>79095</v>
+        <v>89125</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>407868</v>
+        <v>407972</v>
       </c>
       <c r="R9" t="n">
-        <v>6772318</v>
+        <v>6772290</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,32 +1531,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130141199</v>
+        <v>130141085</v>
       </c>
       <c r="B10" t="n">
-        <v>89038</v>
+        <v>95770</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>510</v>
+        <v>2387</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>407972</v>
+        <v>407835</v>
       </c>
       <c r="R10" t="n">
-        <v>6772290</v>
+        <v>6772263</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,32 +1638,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130141085</v>
+        <v>130141157</v>
       </c>
       <c r="B11" t="n">
-        <v>95683</v>
+        <v>79180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2387</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>407835</v>
+        <v>407868</v>
       </c>
       <c r="R11" t="n">
-        <v>6772263</v>
+        <v>6772318</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,45 +1745,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130141058</v>
+        <v>130141056</v>
       </c>
       <c r="B12" t="n">
-        <v>91414</v>
+        <v>57823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3215</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>407891</v>
+        <v>407913</v>
       </c>
       <c r="R12" t="n">
-        <v>6772268</v>
+        <v>6772253</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1820,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1830,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,10 +1857,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130141056</v>
+        <v>130141153</v>
       </c>
       <c r="B13" t="n">
-        <v>57738</v>
+        <v>79180</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,39 +1868,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>407913</v>
+        <v>407802</v>
       </c>
       <c r="R13" t="n">
-        <v>6772253</v>
+        <v>6772259</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1927,7 +1927,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1964,32 +1964,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130141153</v>
+        <v>130141058</v>
       </c>
       <c r="B14" t="n">
-        <v>79095</v>
+        <v>91501</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>3215</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1999,10 +1999,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>407802</v>
+        <v>407891</v>
       </c>
       <c r="R14" t="n">
-        <v>6772259</v>
+        <v>6772268</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2071,32 +2071,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130141066</v>
+        <v>130141165</v>
       </c>
       <c r="B15" t="n">
-        <v>97704</v>
+        <v>79180</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>407860</v>
+        <v>407950</v>
       </c>
       <c r="R15" t="n">
-        <v>6772255</v>
+        <v>6772269</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2178,32 +2178,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130141165</v>
+        <v>130141066</v>
       </c>
       <c r="B16" t="n">
-        <v>79095</v>
+        <v>97791</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2213,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407950</v>
+        <v>407860</v>
       </c>
       <c r="R16" t="n">
-        <v>6772269</v>
+        <v>6772255</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2288,7 +2288,7 @@
         <v>130141149</v>
       </c>
       <c r="B17" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>130141148</v>
       </c>
       <c r="B18" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>130141160</v>
       </c>
       <c r="B19" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>130141158</v>
       </c>
       <c r="B20" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
         <v>130141047</v>
       </c>
       <c r="B21" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>130141036</v>
       </c>
       <c r="B22" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>130141146</v>
       </c>
       <c r="B23" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3034,10 +3034,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130141057</v>
+        <v>130141164</v>
       </c>
       <c r="B24" t="n">
-        <v>57738</v>
+        <v>79180</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3045,39 +3045,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>407845</v>
+        <v>407944</v>
       </c>
       <c r="R24" t="n">
-        <v>6772259</v>
+        <v>6772271</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3109,7 +3104,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3119,7 +3114,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3146,10 +3141,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130141164</v>
+        <v>130141155</v>
       </c>
       <c r="B25" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3181,10 +3176,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>407944</v>
+        <v>407860</v>
       </c>
       <c r="R25" t="n">
-        <v>6772271</v>
+        <v>6772289</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3216,7 +3211,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3226,7 +3221,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3253,10 +3248,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130141155</v>
+        <v>130141057</v>
       </c>
       <c r="B26" t="n">
-        <v>79095</v>
+        <v>57823</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3264,34 +3259,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>407860</v>
+        <v>407845</v>
       </c>
       <c r="R26" t="n">
-        <v>6772289</v>
+        <v>6772259</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3323,7 +3323,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3363,7 +3363,7 @@
         <v>130141154</v>
       </c>
       <c r="B27" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>130141163</v>
       </c>
       <c r="B28" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>130141198</v>
       </c>
       <c r="B29" t="n">
-        <v>89038</v>
+        <v>89125</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 60361-2025 artfynd.xlsx
+++ b/artfynd/A 60361-2025 artfynd.xlsx
@@ -2499,7 +2499,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130141160</v>
+        <v>130141148</v>
       </c>
       <c r="B19" t="n">
         <v>79180</v>
@@ -2534,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>407893</v>
+        <v>407876</v>
       </c>
       <c r="R19" t="n">
-        <v>6772324</v>
+        <v>6772259</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2606,7 +2606,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130141148</v>
+        <v>130141160</v>
       </c>
       <c r="B20" t="n">
         <v>79180</v>
@@ -2641,10 +2641,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>407876</v>
+        <v>407893</v>
       </c>
       <c r="R20" t="n">
-        <v>6772259</v>
+        <v>6772324</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 60361-2025 artfynd.xlsx
+++ b/artfynd/A 60361-2025 artfynd.xlsx
@@ -2499,7 +2499,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130141148</v>
+        <v>130141160</v>
       </c>
       <c r="B19" t="n">
         <v>79180</v>
@@ -2534,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>407876</v>
+        <v>407893</v>
       </c>
       <c r="R19" t="n">
-        <v>6772259</v>
+        <v>6772324</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2606,7 +2606,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130141160</v>
+        <v>130141148</v>
       </c>
       <c r="B20" t="n">
         <v>79180</v>
@@ -2641,10 +2641,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>407893</v>
+        <v>407876</v>
       </c>
       <c r="R20" t="n">
-        <v>6772324</v>
+        <v>6772259</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 60361-2025 artfynd.xlsx
+++ b/artfynd/A 60361-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130141156</v>
+        <v>130141147</v>
       </c>
       <c r="B2" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>407871</v>
+        <v>407893</v>
       </c>
       <c r="R2" t="n">
-        <v>6772300</v>
+        <v>6772248</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130141147</v>
+        <v>130141156</v>
       </c>
       <c r="B3" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>407893</v>
+        <v>407871</v>
       </c>
       <c r="R3" t="n">
-        <v>6772248</v>
+        <v>6772300</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,7 +892,7 @@
         <v>130141152</v>
       </c>
       <c r="B4" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>130141067</v>
       </c>
       <c r="B5" t="n">
-        <v>97791</v>
+        <v>97794</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>130141144</v>
       </c>
       <c r="B6" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>130141161</v>
       </c>
       <c r="B7" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130141199</v>
+        <v>130141162</v>
       </c>
       <c r="B8" t="n">
-        <v>89124</v>
+        <v>79183</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>407972</v>
+        <v>407915</v>
       </c>
       <c r="R8" t="n">
-        <v>6772290</v>
+        <v>6772325</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,32 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130141085</v>
+        <v>130141157</v>
       </c>
       <c r="B9" t="n">
-        <v>95770</v>
+        <v>79183</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2387</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>407835</v>
+        <v>407868</v>
       </c>
       <c r="R9" t="n">
-        <v>6772263</v>
+        <v>6772318</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130141157</v>
+        <v>130141199</v>
       </c>
       <c r="B10" t="n">
-        <v>79180</v>
+        <v>89125</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>407868</v>
+        <v>407972</v>
       </c>
       <c r="R10" t="n">
-        <v>6772318</v>
+        <v>6772290</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,32 +1638,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130141162</v>
+        <v>130141085</v>
       </c>
       <c r="B11" t="n">
-        <v>79180</v>
+        <v>95773</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2387</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>407915</v>
+        <v>407835</v>
       </c>
       <c r="R11" t="n">
-        <v>6772325</v>
+        <v>6772263</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,45 +1745,50 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130141058</v>
+        <v>130141056</v>
       </c>
       <c r="B12" t="n">
-        <v>91501</v>
+        <v>57823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3215</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>407891</v>
+        <v>407913</v>
       </c>
       <c r="R12" t="n">
-        <v>6772268</v>
+        <v>6772253</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1820,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1830,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,32 +1857,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130141153</v>
+        <v>130141058</v>
       </c>
       <c r="B13" t="n">
-        <v>79180</v>
+        <v>91504</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>3215</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1892,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>407802</v>
+        <v>407891</v>
       </c>
       <c r="R13" t="n">
-        <v>6772259</v>
+        <v>6772268</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1927,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1937,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1964,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130141056</v>
+        <v>130141153</v>
       </c>
       <c r="B14" t="n">
-        <v>57823</v>
+        <v>79183</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,39 +1975,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>407913</v>
+        <v>407802</v>
       </c>
       <c r="R14" t="n">
-        <v>6772253</v>
+        <v>6772259</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2071,32 +2071,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130141165</v>
+        <v>130141066</v>
       </c>
       <c r="B15" t="n">
-        <v>79180</v>
+        <v>97794</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>407950</v>
+        <v>407860</v>
       </c>
       <c r="R15" t="n">
-        <v>6772269</v>
+        <v>6772255</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2178,32 +2178,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130141066</v>
+        <v>130141165</v>
       </c>
       <c r="B16" t="n">
-        <v>97791</v>
+        <v>79183</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2213,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407860</v>
+        <v>407950</v>
       </c>
       <c r="R16" t="n">
-        <v>6772255</v>
+        <v>6772269</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2288,7 +2288,7 @@
         <v>130141149</v>
       </c>
       <c r="B17" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2392,10 +2392,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130141158</v>
+        <v>130141148</v>
       </c>
       <c r="B18" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>407887</v>
+        <v>407876</v>
       </c>
       <c r="R18" t="n">
-        <v>6772324</v>
+        <v>6772259</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2502,7 +2502,7 @@
         <v>130141160</v>
       </c>
       <c r="B19" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2606,10 +2606,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130141148</v>
+        <v>130141158</v>
       </c>
       <c r="B20" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2641,10 +2641,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>407876</v>
+        <v>407887</v>
       </c>
       <c r="R20" t="n">
-        <v>6772259</v>
+        <v>6772324</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2716,7 +2716,7 @@
         <v>130141036</v>
       </c>
       <c r="B21" t="n">
-        <v>91692</v>
+        <v>91695</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>130141047</v>
       </c>
       <c r="B22" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>130141146</v>
       </c>
       <c r="B23" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>130141164</v>
       </c>
       <c r="B24" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
         <v>130141155</v>
       </c>
       <c r="B25" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         <v>130141154</v>
       </c>
       <c r="B27" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>130141163</v>
       </c>
       <c r="B28" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>130141198</v>
       </c>
       <c r="B29" t="n">
-        <v>89124</v>
+        <v>89125</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 60361-2025 artfynd.xlsx
+++ b/artfynd/A 60361-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130141147</v>
       </c>
       <c r="B2" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>130141156</v>
       </c>
       <c r="B3" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>130141152</v>
       </c>
       <c r="B4" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>130141067</v>
       </c>
       <c r="B5" t="n">
-        <v>97794</v>
+        <v>97820</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>130141144</v>
       </c>
       <c r="B6" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         <v>130141161</v>
       </c>
       <c r="B7" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1317,32 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130141162</v>
+        <v>130141085</v>
       </c>
       <c r="B8" t="n">
-        <v>79183</v>
+        <v>95799</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2387</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>407915</v>
+        <v>407835</v>
       </c>
       <c r="R8" t="n">
-        <v>6772325</v>
+        <v>6772263</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,7 +1427,7 @@
         <v>130141157</v>
       </c>
       <c r="B9" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1534,7 +1534,7 @@
         <v>130141199</v>
       </c>
       <c r="B10" t="n">
-        <v>89125</v>
+        <v>89151</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1638,32 +1638,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130141085</v>
+        <v>130141162</v>
       </c>
       <c r="B11" t="n">
-        <v>95773</v>
+        <v>79209</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2387</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>407835</v>
+        <v>407915</v>
       </c>
       <c r="R11" t="n">
-        <v>6772263</v>
+        <v>6772325</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130141056</v>
+        <v>130141153</v>
       </c>
       <c r="B12" t="n">
-        <v>57823</v>
+        <v>79209</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1756,39 +1756,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>407913</v>
+        <v>407802</v>
       </c>
       <c r="R12" t="n">
-        <v>6772253</v>
+        <v>6772259</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1830,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1860,7 +1855,7 @@
         <v>130141058</v>
       </c>
       <c r="B13" t="n">
-        <v>91504</v>
+        <v>91530</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1964,10 +1959,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130141153</v>
+        <v>130141056</v>
       </c>
       <c r="B14" t="n">
-        <v>79183</v>
+        <v>57849</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1975,34 +1970,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>407802</v>
+        <v>407913</v>
       </c>
       <c r="R14" t="n">
-        <v>6772259</v>
+        <v>6772253</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2071,32 +2071,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130141066</v>
+        <v>130141165</v>
       </c>
       <c r="B15" t="n">
-        <v>97794</v>
+        <v>79209</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2106,10 +2106,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>407860</v>
+        <v>407950</v>
       </c>
       <c r="R15" t="n">
-        <v>6772255</v>
+        <v>6772269</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2178,32 +2178,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130141165</v>
+        <v>130141066</v>
       </c>
       <c r="B16" t="n">
-        <v>79183</v>
+        <v>97820</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2213,10 +2213,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>407950</v>
+        <v>407860</v>
       </c>
       <c r="R16" t="n">
-        <v>6772269</v>
+        <v>6772255</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2288,7 +2288,7 @@
         <v>130141149</v>
       </c>
       <c r="B17" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,7 +2395,7 @@
         <v>130141148</v>
       </c>
       <c r="B18" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>130141160</v>
       </c>
       <c r="B19" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
         <v>130141158</v>
       </c>
       <c r="B20" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2713,32 +2713,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130141036</v>
+        <v>130141047</v>
       </c>
       <c r="B21" t="n">
-        <v>91695</v>
+        <v>91757</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2748,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>407868</v>
+        <v>407853</v>
       </c>
       <c r="R21" t="n">
-        <v>6772256</v>
+        <v>6772254</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2820,32 +2820,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130141047</v>
+        <v>130141036</v>
       </c>
       <c r="B22" t="n">
-        <v>91731</v>
+        <v>91721</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>407853</v>
+        <v>407868</v>
       </c>
       <c r="R22" t="n">
-        <v>6772254</v>
+        <v>6772256</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2930,7 +2930,7 @@
         <v>130141146</v>
       </c>
       <c r="B23" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3034,10 +3034,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130141164</v>
+        <v>130141057</v>
       </c>
       <c r="B24" t="n">
-        <v>79183</v>
+        <v>57849</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3045,34 +3045,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>407944</v>
+        <v>407845</v>
       </c>
       <c r="R24" t="n">
-        <v>6772271</v>
+        <v>6772259</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3104,7 +3109,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3114,7 +3119,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3141,10 +3146,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130141155</v>
+        <v>130141164</v>
       </c>
       <c r="B25" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3176,10 +3181,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>407860</v>
+        <v>407944</v>
       </c>
       <c r="R25" t="n">
-        <v>6772289</v>
+        <v>6772271</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3211,7 +3216,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3221,7 +3226,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3248,10 +3253,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130141057</v>
+        <v>130141155</v>
       </c>
       <c r="B26" t="n">
-        <v>57823</v>
+        <v>79209</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3259,39 +3264,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>407845</v>
+        <v>407860</v>
       </c>
       <c r="R26" t="n">
-        <v>6772259</v>
+        <v>6772289</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3323,7 +3323,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3363,7 +3363,7 @@
         <v>130141154</v>
       </c>
       <c r="B27" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3470,7 +3470,7 @@
         <v>130141163</v>
       </c>
       <c r="B28" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3577,7 +3577,7 @@
         <v>130141198</v>
       </c>
       <c r="B29" t="n">
-        <v>89125</v>
+        <v>89151</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 60361-2025 artfynd.xlsx
+++ b/artfynd/A 60361-2025 artfynd.xlsx
@@ -1317,32 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130141085</v>
+        <v>130141157</v>
       </c>
       <c r="B8" t="n">
-        <v>95799</v>
+        <v>79209</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2387</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>407835</v>
+        <v>407868</v>
       </c>
       <c r="R8" t="n">
-        <v>6772263</v>
+        <v>6772318</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130141157</v>
+        <v>130141199</v>
       </c>
       <c r="B9" t="n">
-        <v>79209</v>
+        <v>89151</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>407868</v>
+        <v>407972</v>
       </c>
       <c r="R9" t="n">
-        <v>6772318</v>
+        <v>6772290</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,10 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130141199</v>
+        <v>130141162</v>
       </c>
       <c r="B10" t="n">
-        <v>89151</v>
+        <v>79209</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1542,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>407972</v>
+        <v>407915</v>
       </c>
       <c r="R10" t="n">
-        <v>6772290</v>
+        <v>6772325</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,32 +1638,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130141162</v>
+        <v>130141085</v>
       </c>
       <c r="B11" t="n">
-        <v>79209</v>
+        <v>95799</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2387</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>407915</v>
+        <v>407835</v>
       </c>
       <c r="R11" t="n">
-        <v>6772325</v>
+        <v>6772263</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2392,7 +2392,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130141148</v>
+        <v>130141158</v>
       </c>
       <c r="B18" t="n">
         <v>79209</v>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>407876</v>
+        <v>407887</v>
       </c>
       <c r="R18" t="n">
-        <v>6772259</v>
+        <v>6772324</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2499,7 +2499,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130141160</v>
+        <v>130141148</v>
       </c>
       <c r="B19" t="n">
         <v>79209</v>
@@ -2534,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>407893</v>
+        <v>407876</v>
       </c>
       <c r="R19" t="n">
-        <v>6772324</v>
+        <v>6772259</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2606,7 +2606,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130141158</v>
+        <v>130141160</v>
       </c>
       <c r="B20" t="n">
         <v>79209</v>
@@ -2641,7 +2641,7 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>407887</v>
+        <v>407893</v>
       </c>
       <c r="R20" t="n">
         <v>6772324</v>
@@ -2713,32 +2713,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130141047</v>
+        <v>130141036</v>
       </c>
       <c r="B21" t="n">
-        <v>91757</v>
+        <v>91721</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2748,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>407853</v>
+        <v>407868</v>
       </c>
       <c r="R21" t="n">
-        <v>6772254</v>
+        <v>6772256</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2820,32 +2820,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130141036</v>
+        <v>130141047</v>
       </c>
       <c r="B22" t="n">
-        <v>91721</v>
+        <v>91757</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>407868</v>
+        <v>407853</v>
       </c>
       <c r="R22" t="n">
-        <v>6772256</v>
+        <v>6772254</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3034,10 +3034,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130141057</v>
+        <v>130141164</v>
       </c>
       <c r="B24" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3045,39 +3045,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>407845</v>
+        <v>407944</v>
       </c>
       <c r="R24" t="n">
-        <v>6772259</v>
+        <v>6772271</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3109,7 +3104,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3119,7 +3114,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3146,7 +3141,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130141164</v>
+        <v>130141155</v>
       </c>
       <c r="B25" t="n">
         <v>79209</v>
@@ -3181,10 +3176,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>407944</v>
+        <v>407860</v>
       </c>
       <c r="R25" t="n">
-        <v>6772271</v>
+        <v>6772289</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3216,7 +3211,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3226,7 +3221,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3253,10 +3248,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130141155</v>
+        <v>130141057</v>
       </c>
       <c r="B26" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3264,34 +3259,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>407860</v>
+        <v>407845</v>
       </c>
       <c r="R26" t="n">
-        <v>6772289</v>
+        <v>6772259</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3323,7 +3323,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 60361-2025 artfynd.xlsx
+++ b/artfynd/A 60361-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130141147</v>
+        <v>130141156</v>
       </c>
       <c r="B2" t="n">
         <v>79209</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>407893</v>
+        <v>407871</v>
       </c>
       <c r="R2" t="n">
-        <v>6772248</v>
+        <v>6772300</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130141156</v>
+        <v>130141147</v>
       </c>
       <c r="B3" t="n">
         <v>79209</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>407871</v>
+        <v>407893</v>
       </c>
       <c r="R3" t="n">
-        <v>6772300</v>
+        <v>6772248</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -999,7 +999,7 @@
         <v>130141067</v>
       </c>
       <c r="B5" t="n">
-        <v>97820</v>
+        <v>97821</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1317,32 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130141157</v>
+        <v>130141085</v>
       </c>
       <c r="B8" t="n">
-        <v>79209</v>
+        <v>95800</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2387</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>407868</v>
+        <v>407835</v>
       </c>
       <c r="R8" t="n">
-        <v>6772318</v>
+        <v>6772263</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1427,7 +1427,7 @@
         <v>130141199</v>
       </c>
       <c r="B9" t="n">
-        <v>89151</v>
+        <v>89152</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130141162</v>
+        <v>130141157</v>
       </c>
       <c r="B10" t="n">
         <v>79209</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>407915</v>
+        <v>407868</v>
       </c>
       <c r="R10" t="n">
-        <v>6772325</v>
+        <v>6772318</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,32 +1638,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130141085</v>
+        <v>130141162</v>
       </c>
       <c r="B11" t="n">
-        <v>95799</v>
+        <v>79209</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2387</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>407835</v>
+        <v>407915</v>
       </c>
       <c r="R11" t="n">
-        <v>6772263</v>
+        <v>6772325</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,32 +1745,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130141153</v>
+        <v>130141058</v>
       </c>
       <c r="B12" t="n">
-        <v>79209</v>
+        <v>91531</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>3215</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>407802</v>
+        <v>407891</v>
       </c>
       <c r="R12" t="n">
-        <v>6772259</v>
+        <v>6772268</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,32 +1852,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130141058</v>
+        <v>130141153</v>
       </c>
       <c r="B13" t="n">
-        <v>91530</v>
+        <v>79209</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3215</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>407891</v>
+        <v>407802</v>
       </c>
       <c r="R13" t="n">
-        <v>6772268</v>
+        <v>6772259</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2181,7 +2181,7 @@
         <v>130141066</v>
       </c>
       <c r="B16" t="n">
-        <v>97820</v>
+        <v>97821</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130141158</v>
+        <v>130141160</v>
       </c>
       <c r="B18" t="n">
         <v>79209</v>
@@ -2427,7 +2427,7 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>407887</v>
+        <v>407893</v>
       </c>
       <c r="R18" t="n">
         <v>6772324</v>
@@ -2499,7 +2499,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130141148</v>
+        <v>130141158</v>
       </c>
       <c r="B19" t="n">
         <v>79209</v>
@@ -2534,10 +2534,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>407876</v>
+        <v>407887</v>
       </c>
       <c r="R19" t="n">
-        <v>6772259</v>
+        <v>6772324</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2579,7 +2579,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2606,7 +2606,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130141160</v>
+        <v>130141148</v>
       </c>
       <c r="B20" t="n">
         <v>79209</v>
@@ -2641,10 +2641,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>407893</v>
+        <v>407876</v>
       </c>
       <c r="R20" t="n">
-        <v>6772324</v>
+        <v>6772259</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2713,32 +2713,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130141036</v>
+        <v>130141047</v>
       </c>
       <c r="B21" t="n">
-        <v>91721</v>
+        <v>91758</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2748,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>407868</v>
+        <v>407853</v>
       </c>
       <c r="R21" t="n">
-        <v>6772256</v>
+        <v>6772254</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2820,32 +2820,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130141047</v>
+        <v>130141036</v>
       </c>
       <c r="B22" t="n">
-        <v>91757</v>
+        <v>91722</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>407853</v>
+        <v>407868</v>
       </c>
       <c r="R22" t="n">
-        <v>6772254</v>
+        <v>6772256</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3577,7 +3577,7 @@
         <v>130141198</v>
       </c>
       <c r="B29" t="n">
-        <v>89151</v>
+        <v>89152</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 60361-2025 artfynd.xlsx
+++ b/artfynd/A 60361-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130141156</v>
+        <v>130141147</v>
       </c>
       <c r="B2" t="n">
         <v>79209</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>407871</v>
+        <v>407893</v>
       </c>
       <c r="R2" t="n">
-        <v>6772300</v>
+        <v>6772248</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130141147</v>
+        <v>130141156</v>
       </c>
       <c r="B3" t="n">
         <v>79209</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>407893</v>
+        <v>407871</v>
       </c>
       <c r="R3" t="n">
-        <v>6772248</v>
+        <v>6772300</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -999,7 +999,7 @@
         <v>130141067</v>
       </c>
       <c r="B5" t="n">
-        <v>97821</v>
+        <v>97822</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1317,32 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130141085</v>
+        <v>130141199</v>
       </c>
       <c r="B8" t="n">
-        <v>95800</v>
+        <v>89153</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2387</v>
+        <v>510</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>407835</v>
+        <v>407972</v>
       </c>
       <c r="R8" t="n">
-        <v>6772263</v>
+        <v>6772290</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,32 +1424,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130141199</v>
+        <v>130141085</v>
       </c>
       <c r="B9" t="n">
-        <v>89152</v>
+        <v>95801</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>510</v>
+        <v>2387</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>407972</v>
+        <v>407835</v>
       </c>
       <c r="R9" t="n">
-        <v>6772290</v>
+        <v>6772263</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,7 +1531,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130141157</v>
+        <v>130141162</v>
       </c>
       <c r="B10" t="n">
         <v>79209</v>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>407868</v>
+        <v>407915</v>
       </c>
       <c r="R10" t="n">
-        <v>6772318</v>
+        <v>6772325</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1638,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130141162</v>
+        <v>130141157</v>
       </c>
       <c r="B11" t="n">
         <v>79209</v>
@@ -1673,10 +1673,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>407915</v>
+        <v>407868</v>
       </c>
       <c r="R11" t="n">
-        <v>6772325</v>
+        <v>6772318</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1748,7 +1748,7 @@
         <v>130141058</v>
       </c>
       <c r="B12" t="n">
-        <v>91531</v>
+        <v>91532</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130141153</v>
+        <v>130141056</v>
       </c>
       <c r="B13" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1863,34 +1863,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>407802</v>
+        <v>407913</v>
       </c>
       <c r="R13" t="n">
-        <v>6772259</v>
+        <v>6772253</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1927,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1932,7 +1937,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1959,10 +1964,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130141056</v>
+        <v>130141153</v>
       </c>
       <c r="B14" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1970,39 +1975,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>407913</v>
+        <v>407802</v>
       </c>
       <c r="R14" t="n">
-        <v>6772253</v>
+        <v>6772259</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2181,7 +2181,7 @@
         <v>130141066</v>
       </c>
       <c r="B16" t="n">
-        <v>97821</v>
+        <v>97822</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130141160</v>
+        <v>130141148</v>
       </c>
       <c r="B18" t="n">
         <v>79209</v>
@@ -2427,10 +2427,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>407893</v>
+        <v>407876</v>
       </c>
       <c r="R18" t="n">
-        <v>6772324</v>
+        <v>6772259</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2462,7 +2462,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2499,7 +2499,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130141158</v>
+        <v>130141160</v>
       </c>
       <c r="B19" t="n">
         <v>79209</v>
@@ -2534,7 +2534,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>407887</v>
+        <v>407893</v>
       </c>
       <c r="R19" t="n">
         <v>6772324</v>
@@ -2606,7 +2606,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130141148</v>
+        <v>130141158</v>
       </c>
       <c r="B20" t="n">
         <v>79209</v>
@@ -2641,10 +2641,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>407876</v>
+        <v>407887</v>
       </c>
       <c r="R20" t="n">
-        <v>6772259</v>
+        <v>6772324</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2713,32 +2713,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130141047</v>
+        <v>130141036</v>
       </c>
       <c r="B21" t="n">
-        <v>91758</v>
+        <v>91723</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2748,10 +2748,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>407853</v>
+        <v>407868</v>
       </c>
       <c r="R21" t="n">
-        <v>6772254</v>
+        <v>6772256</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2820,32 +2820,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130141036</v>
+        <v>130141047</v>
       </c>
       <c r="B22" t="n">
-        <v>91722</v>
+        <v>91759</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>407868</v>
+        <v>407853</v>
       </c>
       <c r="R22" t="n">
-        <v>6772256</v>
+        <v>6772254</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3034,10 +3034,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130141164</v>
+        <v>130141057</v>
       </c>
       <c r="B24" t="n">
-        <v>79209</v>
+        <v>57849</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3045,34 +3045,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>407944</v>
+        <v>407845</v>
       </c>
       <c r="R24" t="n">
-        <v>6772271</v>
+        <v>6772259</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3104,7 +3109,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3114,7 +3119,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3141,7 +3146,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130141155</v>
+        <v>130141164</v>
       </c>
       <c r="B25" t="n">
         <v>79209</v>
@@ -3176,10 +3181,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>407860</v>
+        <v>407944</v>
       </c>
       <c r="R25" t="n">
-        <v>6772289</v>
+        <v>6772271</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3211,7 +3216,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3221,7 +3226,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3248,10 +3253,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130141057</v>
+        <v>130141155</v>
       </c>
       <c r="B26" t="n">
-        <v>57849</v>
+        <v>79209</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3259,39 +3264,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bergtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>407845</v>
+        <v>407860</v>
       </c>
       <c r="R26" t="n">
-        <v>6772259</v>
+        <v>6772289</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3323,7 +3323,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3577,7 +3577,7 @@
         <v>130141198</v>
       </c>
       <c r="B29" t="n">
-        <v>89152</v>
+        <v>89153</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
